--- a/OrganizedData/2024_organized/error_report.xlsx
+++ b/OrganizedData/2024_organized/error_report.xlsx
@@ -94,41 +94,6 @@
       </c>
     </row>
     <row r="2">
-      <c t="inlineStr">
-        <is>
-          <t>thursday</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>thursday_10430</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>THURS 10430</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>compression</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c t="n">
-        <v>3</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>EXTRA 1 file(s) - check for duplicate runs</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
       <c/>
       <c t="inlineStr">
         <is>
@@ -155,7 +120,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="3">
       <c/>
       <c/>
       <c t="inlineStr">

--- a/OrganizedData/2024_organized/error_report.xlsx
+++ b/OrganizedData/2024_organized/error_report.xlsx
@@ -54,9 +54,15 @@
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
+      <c t="inlineStr" s="1">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
       <c t="inlineStr" s="1">
         <is>
           <t>Day</t>
@@ -94,38 +100,16 @@
       </c>
     </row>
     <row r="2">
-      <c/>
       <c t="inlineStr">
         <is>
-          <t>_unassigned</t>
+          <t>batch1</t>
         </is>
       </c>
-      <c t="inlineStr">
-        <is>
-          <t>Fracture_20250403_165748.is_tens_Exports</t>
-        </is>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>fracture</t>
-        </is>
-      </c>
-      <c/>
-      <c t="n">
-        <v>1</v>
-      </c>
-      <c t="inlineStr">
-        <is>
-          <t>UNASSIGNED - loose export folder does not belong to any sample folder</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
       <c/>
       <c/>
       <c t="inlineStr">
         <is>
-          <t>old</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c/>
